--- a/main/ig/CodeSystem-competence-code-system.xlsx
+++ b/main/ig/CodeSystem-competence-code-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:15:30+00:00</t>
+    <t>2026-07-03T07:35:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-competence-code-system.xlsx
+++ b/main/ig/CodeSystem-competence-code-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:35:49+00:00</t>
+    <t>2026-07-10T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
